--- a/Excels/#Reward.xlsx
+++ b/Excels/#Reward.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -85,6 +85,14 @@
   </si>
   <si>
     <t>rw_gun_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -434,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.54296875" customWidth="1"/>
@@ -445,7 +453,7 @@
     <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -467,8 +475,11 @@
       <c r="G1" t="s">
         <v>13</v>
       </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -490,13 +501,16 @@
       <c r="G2" t="s">
         <v>14</v>
       </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -512,8 +526,11 @@
       <c r="F4">
         <v>1</v>
       </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -528,6 +545,9 @@
       </c>
       <c r="F5">
         <v>1</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
